--- a/协作/模板/26-归档清单.xlsx
+++ b/协作/模板/26-归档清单.xlsx
@@ -2100,11 +2100,11 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
-      <formula1>"表格,文档"</formula1>
-    </dataValidation>
     <dataValidation sqref="J2:J121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
       <formula1>"在档,已迁移,已销毁"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"表格,文档,记录,证据,模板,归档包"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
